--- a/academias/La Materia y sus Interacciones - Estadisticos 20231.xlsx
+++ b/academias/La Materia y sus Interacciones - Estadisticos 20231.xlsx
@@ -551,19 +551,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>23</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1">
-        <v>59</v>
+        <v>60.5</v>
       </c>
       <c r="H3" s="1">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="I3" s="2">
         <v>6.3</v>
@@ -586,19 +586,19 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>14</v>
       </c>
       <c r="G4" s="1">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="I4" s="2">
         <v>6.7</v>
@@ -656,28 +656,28 @@
         <v>20</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>12</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1">
-        <v>66.7</v>
+        <v>63.2</v>
       </c>
       <c r="H6" s="1">
-        <v>33.3</v>
+        <v>36.8</v>
       </c>
       <c r="I6" s="2">
         <v>6.6</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -688,28 +688,28 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E7">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F7">
         <v>75</v>
       </c>
       <c r="G7" s="1">
-        <v>55.9</v>
+        <v>55.6</v>
       </c>
       <c r="H7" s="1">
-        <v>44.1</v>
+        <v>44.4</v>
       </c>
       <c r="I7" s="2">
         <v>6.3</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -793,19 +793,19 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10">
         <v>14</v>
       </c>
       <c r="F10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10" s="1">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="H10" s="1">
-        <v>58.8</v>
+        <v>60</v>
       </c>
       <c r="I10" s="2">
         <v>6</v>
@@ -828,19 +828,19 @@
         <v>24</v>
       </c>
       <c r="D11">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F11">
         <v>21</v>
       </c>
       <c r="G11" s="1">
-        <v>46.2</v>
+        <v>47.5</v>
       </c>
       <c r="H11" s="1">
-        <v>53.8</v>
+        <v>52.5</v>
       </c>
       <c r="I11" s="2">
         <v>5.9</v>
@@ -930,19 +930,19 @@
         <v>14</v>
       </c>
       <c r="D14">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E14">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F14">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G14" s="1">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="H14" s="1">
-        <v>60.1</v>
+        <v>60</v>
       </c>
       <c r="I14" s="2">
         <v>5.8</v>
@@ -959,28 +959,28 @@
         <v>15</v>
       </c>
       <c r="D15">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E15">
         <v>172</v>
       </c>
       <c r="F15">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G15" s="1">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
       <c r="H15" s="1">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
       <c r="I15" s="2">
         <v>6</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -1080,13 +1080,13 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K3" s="1">
         <v>100</v>
@@ -1115,13 +1115,13 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K4" s="1">
         <v>100</v>
@@ -1185,13 +1185,13 @@
         <v>20</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -1217,13 +1217,13 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -1322,13 +1322,13 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1340,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1357,13 +1357,13 @@
         <v>24</v>
       </c>
       <c r="D11">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -1459,13 +1459,13 @@
         <v>14</v>
       </c>
       <c r="D14">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -1488,13 +1488,13 @@
         <v>15</v>
       </c>
       <c r="D15">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -1609,19 +1609,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>23</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1">
-        <v>59</v>
+        <v>60.5</v>
       </c>
       <c r="H3" s="1">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="I3" s="2">
         <v>6.3</v>
@@ -1644,19 +1644,19 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>14</v>
       </c>
       <c r="G4" s="1">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="I4" s="2">
         <v>6.7</v>
@@ -1714,28 +1714,28 @@
         <v>20</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>12</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1">
-        <v>66.7</v>
+        <v>63.2</v>
       </c>
       <c r="H6" s="1">
-        <v>33.3</v>
+        <v>36.8</v>
       </c>
       <c r="I6" s="2">
         <v>6.6</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1746,28 +1746,28 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E7">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F7">
         <v>75</v>
       </c>
       <c r="G7" s="1">
-        <v>55.9</v>
+        <v>55.6</v>
       </c>
       <c r="H7" s="1">
-        <v>44.1</v>
+        <v>44.4</v>
       </c>
       <c r="I7" s="2">
         <v>6.3</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1851,19 +1851,19 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10">
         <v>14</v>
       </c>
       <c r="F10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10" s="1">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="H10" s="1">
-        <v>58.8</v>
+        <v>60</v>
       </c>
       <c r="I10" s="2">
         <v>6.1</v>
@@ -1886,19 +1886,19 @@
         <v>24</v>
       </c>
       <c r="D11">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F11">
         <v>21</v>
       </c>
       <c r="G11" s="1">
-        <v>46.2</v>
+        <v>47.5</v>
       </c>
       <c r="H11" s="1">
-        <v>53.8</v>
+        <v>52.5</v>
       </c>
       <c r="I11" s="2">
         <v>6</v>
@@ -1988,19 +1988,19 @@
         <v>14</v>
       </c>
       <c r="D14">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E14">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F14">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G14" s="1">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="H14" s="1">
-        <v>60.1</v>
+        <v>60</v>
       </c>
       <c r="I14" s="2">
         <v>5.8</v>
@@ -2017,28 +2017,28 @@
         <v>15</v>
       </c>
       <c r="D15">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E15">
         <v>172</v>
       </c>
       <c r="F15">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G15" s="1">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
       <c r="H15" s="1">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
       <c r="I15" s="2">
         <v>6.1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/academias/La Materia y sus Interacciones - Estadisticos 20231.xlsx
+++ b/academias/La Materia y sus Interacciones - Estadisticos 20231.xlsx
@@ -551,19 +551,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3">
         <v>23</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1">
-        <v>60.5</v>
+        <v>59</v>
       </c>
       <c r="H3" s="1">
-        <v>39.5</v>
+        <v>41</v>
       </c>
       <c r="I3" s="2">
         <v>6.3</v>
@@ -659,25 +659,25 @@
         <v>19</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>63.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>36.8</v>
+        <v>31.6</v>
       </c>
       <c r="I6" s="2">
         <v>6.6</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -688,28 +688,28 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F7">
         <v>75</v>
       </c>
       <c r="G7" s="1">
-        <v>55.6</v>
+        <v>55.9</v>
       </c>
       <c r="H7" s="1">
-        <v>44.4</v>
+        <v>44.1</v>
       </c>
       <c r="I7" s="2">
         <v>6.3</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -793,19 +793,19 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10">
         <v>14</v>
       </c>
       <c r="F10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G10" s="1">
-        <v>40</v>
+        <v>41.2</v>
       </c>
       <c r="H10" s="1">
-        <v>60</v>
+        <v>58.8</v>
       </c>
       <c r="I10" s="2">
         <v>6</v>
@@ -930,19 +930,19 @@
         <v>14</v>
       </c>
       <c r="D14">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E14">
         <v>78</v>
       </c>
       <c r="F14">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G14" s="1">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="H14" s="1">
-        <v>60</v>
+        <v>59.8</v>
       </c>
       <c r="I14" s="2">
         <v>5.8</v>
@@ -962,25 +962,25 @@
         <v>364</v>
       </c>
       <c r="E15">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F15">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G15" s="1">
-        <v>47.3</v>
+        <v>47.5</v>
       </c>
       <c r="H15" s="1">
-        <v>52.7</v>
+        <v>52.5</v>
       </c>
       <c r="I15" s="2">
         <v>6</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1048,25 +1048,25 @@
         <v>36</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>36.1</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>63.9</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1080,13 +1080,13 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K3" s="1">
         <v>100</v>
@@ -1188,25 +1188,25 @@
         <v>19</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>36.8</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1217,28 +1217,28 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>85.3</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J7">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1255,25 +1255,25 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J8">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1290,25 +1290,25 @@
         <v>24</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J9">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1322,28 +1322,28 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F10">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>61.8</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>38.2</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J10">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1360,25 +1360,25 @@
         <v>40</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>57.5</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>42.5</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J11">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1395,25 +1395,25 @@
         <v>39</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>46.2</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>53.8</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J12">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1430,25 +1430,25 @@
         <v>30</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F13">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>36.7</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>63.3</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J13">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1459,28 +1459,28 @@
         <v>14</v>
       </c>
       <c r="D14">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="F14">
-        <v>195</v>
+        <v>101</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>47.9</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>52.1</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J14">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1491,25 +1491,25 @@
         <v>364</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="F15">
-        <v>364</v>
+        <v>246</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>32.4</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J15">
-        <v>364</v>
+        <v>115</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>31.6</v>
       </c>
     </row>
   </sheetData>
@@ -1577,19 +1577,19 @@
         <v>36</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1">
-        <v>38.9</v>
+        <v>36.1</v>
       </c>
       <c r="H2" s="1">
-        <v>61.1</v>
+        <v>63.9</v>
       </c>
       <c r="I2" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1609,19 +1609,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3">
         <v>23</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1">
-        <v>60.5</v>
+        <v>59</v>
       </c>
       <c r="H3" s="1">
-        <v>39.5</v>
+        <v>41</v>
       </c>
       <c r="I3" s="2">
         <v>6.3</v>
@@ -1729,13 +1729,13 @@
         <v>36.8</v>
       </c>
       <c r="I6" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1746,28 +1746,28 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E7">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F7">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G7" s="1">
-        <v>55.6</v>
+        <v>54.7</v>
       </c>
       <c r="H7" s="1">
-        <v>44.4</v>
+        <v>45.3</v>
       </c>
       <c r="I7" s="2">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1784,19 +1784,19 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1">
-        <v>44.4</v>
+        <v>37</v>
       </c>
       <c r="H8" s="1">
-        <v>55.6</v>
+        <v>63</v>
       </c>
       <c r="I8" s="2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1819,19 +1819,19 @@
         <v>24</v>
       </c>
       <c r="E9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9" s="1">
-        <v>37.5</v>
+        <v>41.7</v>
       </c>
       <c r="H9" s="1">
-        <v>62.5</v>
+        <v>58.3</v>
       </c>
       <c r="I9" s="2">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1851,22 +1851,22 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F10">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G10" s="1">
-        <v>40</v>
+        <v>61.8</v>
       </c>
       <c r="H10" s="1">
-        <v>60</v>
+        <v>38.2</v>
       </c>
       <c r="I10" s="2">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1889,19 +1889,19 @@
         <v>40</v>
       </c>
       <c r="E11">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G11" s="1">
-        <v>47.5</v>
+        <v>57.5</v>
       </c>
       <c r="H11" s="1">
-        <v>52.5</v>
+        <v>42.5</v>
       </c>
       <c r="I11" s="2">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1924,19 +1924,19 @@
         <v>39</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G12" s="1">
-        <v>38.5</v>
+        <v>46.2</v>
       </c>
       <c r="H12" s="1">
-        <v>61.5</v>
+        <v>53.8</v>
       </c>
       <c r="I12" s="2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1959,19 +1959,19 @@
         <v>30</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F13">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G13" s="1">
-        <v>30</v>
+        <v>36.7</v>
       </c>
       <c r="H13" s="1">
-        <v>70</v>
+        <v>63.3</v>
       </c>
       <c r="I13" s="2">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1988,22 +1988,22 @@
         <v>14</v>
       </c>
       <c r="D14">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E14">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="F14">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="G14" s="1">
-        <v>40</v>
+        <v>47.9</v>
       </c>
       <c r="H14" s="1">
-        <v>60</v>
+        <v>52.1</v>
       </c>
       <c r="I14" s="2">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2020,25 +2020,25 @@
         <v>364</v>
       </c>
       <c r="E15">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="F15">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="G15" s="1">
-        <v>47.3</v>
+        <v>51.1</v>
       </c>
       <c r="H15" s="1">
-        <v>52.7</v>
+        <v>48.9</v>
       </c>
       <c r="I15" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/La Materia y sus Interacciones - Estadisticos 20231.xlsx
+++ b/academias/La Materia y sus Interacciones - Estadisticos 20231.xlsx
@@ -1083,25 +1083,25 @@
         <v>39</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>43.6</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1118,25 +1118,25 @@
         <v>39</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>61.5</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>38.5</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1153,25 +1153,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>59.5</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1220,25 +1220,25 @@
         <v>170</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="F7">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="G7" s="1">
-        <v>14.7</v>
+        <v>50.6</v>
       </c>
       <c r="H7" s="1">
-        <v>85.3</v>
+        <v>49.4</v>
       </c>
       <c r="I7" s="2">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>67.59999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1491,25 +1491,25 @@
         <v>364</v>
       </c>
       <c r="E15">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="F15">
-        <v>246</v>
+        <v>185</v>
       </c>
       <c r="G15" s="1">
-        <v>32.4</v>
+        <v>49.2</v>
       </c>
       <c r="H15" s="1">
-        <v>67.59999999999999</v>
+        <v>50.8</v>
       </c>
       <c r="I15" s="2">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="J15">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>31.6</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1612,19 +1612,19 @@
         <v>39</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1">
-        <v>59</v>
+        <v>56.4</v>
       </c>
       <c r="H3" s="1">
-        <v>41</v>
+        <v>43.6</v>
       </c>
       <c r="I3" s="2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1647,19 +1647,19 @@
         <v>39</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1">
-        <v>64.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="H4" s="1">
-        <v>35.9</v>
+        <v>38.5</v>
       </c>
       <c r="I4" s="2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1682,16 +1682,16 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G5" s="1">
-        <v>54.1</v>
+        <v>40.5</v>
       </c>
       <c r="H5" s="1">
-        <v>45.9</v>
+        <v>59.5</v>
       </c>
       <c r="I5" s="2">
         <v>5.9</v>
@@ -1749,16 +1749,16 @@
         <v>170</v>
       </c>
       <c r="E7">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F7">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G7" s="1">
-        <v>54.7</v>
+        <v>50.6</v>
       </c>
       <c r="H7" s="1">
-        <v>45.3</v>
+        <v>49.4</v>
       </c>
       <c r="I7" s="2">
         <v>6.4</v>
@@ -2020,16 +2020,16 @@
         <v>364</v>
       </c>
       <c r="E15">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F15">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="G15" s="1">
-        <v>51.1</v>
+        <v>49.2</v>
       </c>
       <c r="H15" s="1">
-        <v>48.9</v>
+        <v>50.8</v>
       </c>
       <c r="I15" s="2">
         <v>6.3</v>

--- a/academias/La Materia y sus Interacciones - Estadisticos 20231.xlsx
+++ b/academias/La Materia y sus Interacciones - Estadisticos 20231.xlsx
@@ -1577,19 +1577,19 @@
         <v>36</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1">
-        <v>36.1</v>
+        <v>72.2</v>
       </c>
       <c r="H2" s="1">
-        <v>63.9</v>
+        <v>27.8</v>
       </c>
       <c r="I2" s="2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1612,19 +1612,19 @@
         <v>39</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>56.4</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>43.6</v>
+        <v>15.4</v>
       </c>
       <c r="I3" s="2">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1647,19 +1647,19 @@
         <v>39</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>61.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>38.5</v>
+        <v>23.1</v>
       </c>
       <c r="I4" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1682,19 +1682,19 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1">
-        <v>40.5</v>
+        <v>48.6</v>
       </c>
       <c r="H5" s="1">
-        <v>59.5</v>
+        <v>51.4</v>
       </c>
       <c r="I5" s="2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1717,19 +1717,19 @@
         <v>19</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>63.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>36.8</v>
+        <v>21.1</v>
       </c>
       <c r="I6" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1749,19 +1749,19 @@
         <v>170</v>
       </c>
       <c r="E7">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="F7">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="G7" s="1">
-        <v>50.6</v>
+        <v>71.8</v>
       </c>
       <c r="H7" s="1">
-        <v>49.4</v>
+        <v>28.2</v>
       </c>
       <c r="I7" s="2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1784,19 +1784,19 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1">
-        <v>37</v>
+        <v>48.1</v>
       </c>
       <c r="H8" s="1">
-        <v>63</v>
+        <v>51.9</v>
       </c>
       <c r="I8" s="2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1854,19 +1854,19 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1">
-        <v>61.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>38.2</v>
+        <v>32.4</v>
       </c>
       <c r="I10" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1889,16 +1889,16 @@
         <v>40</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G11" s="1">
-        <v>57.5</v>
+        <v>75</v>
       </c>
       <c r="H11" s="1">
-        <v>42.5</v>
+        <v>25</v>
       </c>
       <c r="I11" s="2">
         <v>6.5</v>
@@ -1924,19 +1924,19 @@
         <v>39</v>
       </c>
       <c r="E12">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>46.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>53.8</v>
+        <v>25.6</v>
       </c>
       <c r="I12" s="2">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1959,19 +1959,19 @@
         <v>30</v>
       </c>
       <c r="E13">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>36.7</v>
+        <v>66.7</v>
       </c>
       <c r="H13" s="1">
-        <v>63.3</v>
+        <v>33.3</v>
       </c>
       <c r="I13" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1991,19 +1991,19 @@
         <v>194</v>
       </c>
       <c r="E14">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F14">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="G14" s="1">
-        <v>47.9</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>52.1</v>
+        <v>35.6</v>
       </c>
       <c r="I14" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2020,19 +2020,19 @@
         <v>364</v>
       </c>
       <c r="E15">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="F15">
-        <v>185</v>
+        <v>117</v>
       </c>
       <c r="G15" s="1">
-        <v>49.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>50.8</v>
+        <v>32.1</v>
       </c>
       <c r="I15" s="2">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="J15">
         <v>0</v>

--- a/academias/La Materia y sus Interacciones - Estadisticos 20231.xlsx
+++ b/academias/La Materia y sus Interacciones - Estadisticos 20231.xlsx
@@ -1924,16 +1924,16 @@
         <v>39</v>
       </c>
       <c r="E12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1">
-        <v>74.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>25.6</v>
+        <v>23.1</v>
       </c>
       <c r="I12" s="2">
         <v>6.5</v>
@@ -1991,16 +1991,16 @@
         <v>194</v>
       </c>
       <c r="E14">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F14">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G14" s="1">
-        <v>64.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="I14" s="2">
         <v>6.3</v>
@@ -2020,16 +2020,16 @@
         <v>364</v>
       </c>
       <c r="E15">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F15">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G15" s="1">
-        <v>67.90000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>32.1</v>
+        <v>31.9</v>
       </c>
       <c r="I15" s="2">
         <v>6.4</v>

--- a/academias/La Materia y sus Interacciones - Estadisticos 20231.xlsx
+++ b/academias/La Materia y sus Interacciones - Estadisticos 20231.xlsx
@@ -1589,7 +1589,7 @@
         <v>27.8</v>
       </c>
       <c r="I2" s="2">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>15.4</v>
       </c>
       <c r="I3" s="2">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>23.1</v>
       </c>
       <c r="I4" s="2">
-        <v>6.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1694,7 +1694,7 @@
         <v>51.4</v>
       </c>
       <c r="I5" s="2">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>21.1</v>
       </c>
       <c r="I6" s="2">
-        <v>6.9</v>
+        <v>8.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>28.2</v>
       </c>
       <c r="I7" s="2">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1796,7 +1796,7 @@
         <v>51.9</v>
       </c>
       <c r="I8" s="2">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1831,7 +1831,7 @@
         <v>58.3</v>
       </c>
       <c r="I9" s="2">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>32.4</v>
       </c>
       <c r="I10" s="2">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1901,7 +1901,7 @@
         <v>25</v>
       </c>
       <c r="I11" s="2">
-        <v>6.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>23.1</v>
       </c>
       <c r="I12" s="2">
-        <v>6.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1971,7 +1971,7 @@
         <v>33.3</v>
       </c>
       <c r="I13" s="2">
-        <v>6.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2003,7 +2003,7 @@
         <v>35.1</v>
       </c>
       <c r="I14" s="2">
-        <v>6.3</v>
+        <v>8.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2032,7 +2032,7 @@
         <v>31.9</v>
       </c>
       <c r="I15" s="2">
-        <v>6.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J15">
         <v>0</v>

--- a/academias/La Materia y sus Interacciones - Estadisticos 20231.xlsx
+++ b/academias/La Materia y sus Interacciones - Estadisticos 20231.xlsx
@@ -1589,7 +1589,7 @@
         <v>27.8</v>
       </c>
       <c r="I2" s="2">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>15.4</v>
       </c>
       <c r="I3" s="2">
-        <v>9.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>23.1</v>
       </c>
       <c r="I4" s="2">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1694,7 +1694,7 @@
         <v>51.4</v>
       </c>
       <c r="I5" s="2">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>21.1</v>
       </c>
       <c r="I6" s="2">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>28.2</v>
       </c>
       <c r="I7" s="2">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1796,7 +1796,7 @@
         <v>51.9</v>
       </c>
       <c r="I8" s="2">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1831,7 +1831,7 @@
         <v>58.3</v>
       </c>
       <c r="I9" s="2">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>32.4</v>
       </c>
       <c r="I10" s="2">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1901,7 +1901,7 @@
         <v>25</v>
       </c>
       <c r="I11" s="2">
-        <v>8.800000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>23.1</v>
       </c>
       <c r="I12" s="2">
-        <v>8.800000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1971,7 +1971,7 @@
         <v>33.3</v>
       </c>
       <c r="I13" s="2">
-        <v>8.300000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2003,7 +2003,7 @@
         <v>35.1</v>
       </c>
       <c r="I14" s="2">
-        <v>8.1</v>
+        <v>6.3</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2032,7 +2032,7 @@
         <v>31.9</v>
       </c>
       <c r="I15" s="2">
-        <v>8.300000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="J15">
         <v>0</v>
